--- a/static_benchmark_results.xlsx
+++ b/static_benchmark_results.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0005580840006587096</v>
+        <v>0.0006549170011567185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01756129300338216</v>
+        <v>1.76022353904591</v>
       </c>
       <c r="E2" t="n">
-        <v>4.084958397463966e-05</v>
+        <v>4.02573375744454e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>1.001571335371169</v>
+        <v>1.001522479945697</v>
       </c>
       <c r="G2" t="n">
-        <v>1.015036593320967</v>
+        <v>1.014800278777046</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.01249275099780789</v>
+        <v>0.01367803799439571</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07702923601027578</v>
+        <v>7.581022457014114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004210310971136541</v>
+        <v>0.0004298506741552357</v>
       </c>
       <c r="F3" t="n">
-        <v>1.014858421006316</v>
+        <v>1.015216409169157</v>
       </c>
       <c r="G3" t="n">
-        <v>1.044088461672073</v>
+        <v>1.043825646890622</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0005580840006587096</v>
+        <v>0.0006549170011567185</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01779809000618116</v>
+        <v>1.762463029146602</v>
       </c>
       <c r="E4" t="n">
-        <v>4.094177186214845e-05</v>
+        <v>3.949241769017395e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>1.00160005310515</v>
+        <v>1.001518197221732</v>
       </c>
       <c r="G4" t="n">
-        <v>1.015298851296311</v>
+        <v>1.014707891100917</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.001387708000038401</v>
+        <v>0.001312375001361943</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03677293898454081</v>
+        <v>3.774447022469758</v>
       </c>
       <c r="E5" t="n">
-        <v>3.336493144633645e-05</v>
+        <v>3.478352383354353e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>1.001364809401446</v>
+        <v>1.001401504698528</v>
       </c>
       <c r="G5" t="n">
-        <v>1.024087972564616</v>
+        <v>1.025492464144651</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02401199600353721</v>
+        <v>0.02398842098773457</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1235944699919855</v>
+        <v>12.2741273730353</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000475024009559138</v>
+        <v>0.0004378212406714243</v>
       </c>
       <c r="F6" t="n">
-        <v>1.016659692768095</v>
+        <v>1.016631397027611</v>
       </c>
       <c r="G6" t="n">
-        <v>1.038820788573066</v>
+        <v>1.03515969738224</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.001387708000038401</v>
+        <v>0.001312375001361943</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03746876501190854</v>
+        <v>3.83782281297681</v>
       </c>
       <c r="E7" t="n">
-        <v>3.823025151427852e-05</v>
+        <v>3.712358709789627e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>1.001656135020252</v>
+        <v>1.001558329317493</v>
       </c>
       <c r="G7" t="n">
-        <v>1.042157751072817</v>
+        <v>1.048131932257293</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001973999999790976</v>
+        <v>0.004934165999657125</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3290826229858794</v>
+        <v>33.03037058909831</v>
       </c>
       <c r="E8" t="n">
-        <v>4.732999999999999e-08</v>
+        <v>0.0002437043585</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1.010411572520871</v>
+        <v>1.013077361431308</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.001973999999790976</v>
+        <v>0.004934165999657125</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06677187899640558</v>
+        <v>6.585742769999342</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -722,19 +722,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001973999999790976</v>
+        <v>0.004934165999657125</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3285575769959905</v>
+        <v>32.9237858644774</v>
       </c>
       <c r="E10" t="n">
-        <v>3.94935e-05</v>
+        <v>6.733480649999999e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>1710</v>
+        <v>14080</v>
       </c>
       <c r="G10" t="n">
-        <v>87860.99999999999</v>
+        <v>88850</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0008978329997262335</v>
+        <v>0.0006825829987064935</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01223724401552317</v>
+        <v>1.338603053138286</v>
       </c>
       <c r="E11" t="n">
-        <v>0.008399372923071281</v>
+        <v>0.007904886559125007</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>30825171.13169752</v>
+        <v>31853194.38151336</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0008978329997262335</v>
+        <v>0.0006825829987064935</v>
       </c>
       <c r="D12" t="n">
-        <v>0.004660840011638356</v>
+        <v>0.480374750757619</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0008978329997262335</v>
+        <v>0.0006825829987064935</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01209960199685156</v>
+        <v>1.338133700000981</v>
       </c>
       <c r="E13" t="n">
-        <v>0.009956342524227339</v>
+        <v>0.01049828357292688</v>
       </c>
       <c r="F13" t="n">
-        <v>1102.153229844767</v>
+        <v>1413.683733574988</v>
       </c>
       <c r="G13" t="n">
-        <v>16499558.63795693</v>
+        <v>18157781.10557314</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0001588330005688476</v>
+        <v>0.0001499579993833322</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0162199090109425</v>
+        <v>1.709128216989484</v>
       </c>
       <c r="E14" t="n">
-        <v>4.361482763267963e-05</v>
+        <v>4.531431036434613e-05</v>
       </c>
       <c r="F14" t="n">
-        <v>1.001715535062607</v>
+        <v>1.001753602870911</v>
       </c>
       <c r="G14" t="n">
-        <v>1.01529613507004</v>
+        <v>1.015412804389388</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.009773081001185346</v>
+        <v>0.009814751989324577</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07244831701063958</v>
+        <v>7.353260704758213</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0004819171780404262</v>
+        <v>0.0004436711479732811</v>
       </c>
       <c r="F15" t="n">
-        <v>1.017178256250824</v>
+        <v>1.015947744020477</v>
       </c>
       <c r="G15" t="n">
-        <v>1.049546350499713</v>
+        <v>1.047052192669214</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -902,19 +902,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0001588330005688476</v>
+        <v>0.0001499579993833322</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01653524399080197</v>
+        <v>1.747170383023331</v>
       </c>
       <c r="E16" t="n">
-        <v>4.282071414629603e-05</v>
+        <v>4.373461394878706e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>1.001721791659181</v>
+        <v>1.001694128852967</v>
       </c>
       <c r="G16" t="n">
-        <v>1.015196265774933</v>
+        <v>1.015138405954477</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>

--- a/static_benchmark_results.xlsx
+++ b/static_benchmark_results.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0006549170011567185</v>
+        <v>0.001110041001084028</v>
       </c>
       <c r="D2" t="n">
-        <v>1.76022353904591</v>
+        <v>6.604945031758689</v>
       </c>
       <c r="E2" t="n">
-        <v>4.02573375744454e-05</v>
+        <v>2.864899779119949e-06</v>
       </c>
       <c r="F2" t="n">
-        <v>1.001522479945697</v>
+        <v>1.000106350978969</v>
       </c>
       <c r="G2" t="n">
-        <v>1.014800278777046</v>
+        <v>1.001196446824426</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.01367803799439571</v>
+        <v>0.04185245703047258</v>
       </c>
       <c r="D3" t="n">
-        <v>7.581022457014114</v>
+        <v>20.19460271931166</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004298506741552357</v>
+        <v>0.0005223702775757396</v>
       </c>
       <c r="F3" t="n">
-        <v>1.015216409169157</v>
+        <v>1.021227605112106</v>
       </c>
       <c r="G3" t="n">
-        <v>1.043825646890622</v>
+        <v>1.037037789200652</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -542,19 +542,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0006549170011567185</v>
+        <v>0.001110041001084028</v>
       </c>
       <c r="D4" t="n">
-        <v>1.762463029146602</v>
+        <v>6.681295995687833</v>
       </c>
       <c r="E4" t="n">
-        <v>3.949241769017395e-05</v>
+        <v>2.92653325332654e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>1.001518197221732</v>
+        <v>1.000111854690093</v>
       </c>
       <c r="G4" t="n">
-        <v>1.014707891100917</v>
+        <v>1.001061761149935</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.001312375001361943</v>
+        <v>0.0009762499994394602</v>
       </c>
       <c r="D5" t="n">
-        <v>3.774447022469758</v>
+        <v>14.65774078363029</v>
       </c>
       <c r="E5" t="n">
-        <v>3.478352383354353e-05</v>
+        <v>3.715220035981929e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>1.001401504698528</v>
+        <v>1.000095340693586</v>
       </c>
       <c r="G5" t="n">
-        <v>1.025492464144651</v>
+        <v>1.001490400046632</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02398842098773457</v>
+        <v>0.08562703502866498</v>
       </c>
       <c r="D6" t="n">
-        <v>12.2741273730353</v>
+        <v>39.54234380089656</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0004378212406714243</v>
+        <v>0.0004477996735226112</v>
       </c>
       <c r="F6" t="n">
-        <v>1.016631397027611</v>
+        <v>1.016640410436328</v>
       </c>
       <c r="G6" t="n">
-        <v>1.03515969738224</v>
+        <v>1.029620461747061</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.001312375001361943</v>
+        <v>0.0009762499994394602</v>
       </c>
       <c r="D7" t="n">
-        <v>3.83782281297681</v>
+        <v>14.80521248383047</v>
       </c>
       <c r="E7" t="n">
-        <v>3.712358709789627e-05</v>
+        <v>5.1009523241982e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>1.001558329317493</v>
+        <v>1.000118145388798</v>
       </c>
       <c r="G7" t="n">
-        <v>1.048131932257293</v>
+        <v>1.008071251938363</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.004934165999657125</v>
+        <v>0.002445458998408867</v>
       </c>
       <c r="D8" t="n">
-        <v>33.03037058909831</v>
+        <v>33.49476269399747</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002437043585</v>
+        <v>0.000278421957715</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.000801587732709</v>
       </c>
       <c r="G8" t="n">
-        <v>1.013077361431308</v>
+        <v>1.1</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.004934165999657125</v>
+        <v>0.03329875300732965</v>
       </c>
       <c r="D9" t="n">
-        <v>6.585742769999342</v>
+        <v>17.16311608316391</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3.271071802420226e-07</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>1.015209178436276</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -722,19 +722,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.004934165999657125</v>
+        <v>0.002445458998408867</v>
       </c>
       <c r="D10" t="n">
-        <v>32.9237858644774</v>
+        <v>33.43525759114527</v>
       </c>
       <c r="E10" t="n">
-        <v>6.733480649999999e-05</v>
+        <v>2.6812991105e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>14080</v>
+        <v>2.617448999230177</v>
       </c>
       <c r="G10" t="n">
-        <v>88850</v>
+        <v>17.50341666666665</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0006825829987064935</v>
+        <v>0.0009363339995616116</v>
       </c>
       <c r="D11" t="n">
-        <v>1.338603053138286</v>
+        <v>7.723917829962375</v>
       </c>
       <c r="E11" t="n">
-        <v>0.007904886559125007</v>
+        <v>0.001192861536610422</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>31853194.38151336</v>
+        <v>1.006151642974233</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -782,19 +782,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0006825829987064935</v>
+        <v>0.00308658399808337</v>
       </c>
       <c r="D12" t="n">
-        <v>0.480374750757619</v>
+        <v>2.359730607036909</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.0004782867563549551</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>1.047125718437318</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0006825829987064935</v>
+        <v>0.0009363339995616116</v>
       </c>
       <c r="D13" t="n">
-        <v>1.338133700000981</v>
+        <v>7.769917972951589</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01049828357292688</v>
+        <v>0.002260638748482831</v>
       </c>
       <c r="F13" t="n">
-        <v>1413.683733574988</v>
+        <v>122.0843672456576</v>
       </c>
       <c r="G13" t="n">
-        <v>18157781.10557314</v>
+        <v>364.4747725392886</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0001499579993833322</v>
+        <v>0.0004159170002822066</v>
       </c>
       <c r="D14" t="n">
-        <v>1.709128216989484</v>
+        <v>6.578013333639319</v>
       </c>
       <c r="E14" t="n">
-        <v>4.531431036434613e-05</v>
+        <v>2.940499397035262e-06</v>
       </c>
       <c r="F14" t="n">
-        <v>1.001753602870911</v>
+        <v>1.000108864146786</v>
       </c>
       <c r="G14" t="n">
-        <v>1.015412804389388</v>
+        <v>1.001178189953486</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.009814751989324577</v>
+        <v>0.04131762100951164</v>
       </c>
       <c r="D15" t="n">
-        <v>7.353260704758213</v>
+        <v>19.49141900302311</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0004436711479732811</v>
+        <v>0.0002923076035169973</v>
       </c>
       <c r="F15" t="n">
-        <v>1.015947744020477</v>
+        <v>1.010943380605078</v>
       </c>
       <c r="G15" t="n">
-        <v>1.047052192669214</v>
+        <v>1.026192550733684</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -902,19 +902,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0001499579993833322</v>
+        <v>0.0004159170002822066</v>
       </c>
       <c r="D16" t="n">
-        <v>1.747170383023331</v>
+        <v>6.710400104020664</v>
       </c>
       <c r="E16" t="n">
-        <v>4.373461394878706e-05</v>
+        <v>2.925594506810903e-06</v>
       </c>
       <c r="F16" t="n">
-        <v>1.001694128852967</v>
+        <v>1.000111577514675</v>
       </c>
       <c r="G16" t="n">
-        <v>1.015138405954477</v>
+        <v>1.001020979345522</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
